--- a/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_LOBE HUESCA LA MAGIA.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_LOBE HUESCA LA MAGIA.xlsx
@@ -565,67 +565,67 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3531</v>
+        <v>3.4481</v>
       </c>
       <c r="E2" t="n">
-        <v>4.3397</v>
+        <v>4.6914</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.9865999999999997</v>
+        <v>-1.2432</v>
       </c>
       <c r="G2" t="n">
-        <v>4.958699999999999</v>
+        <v>4.969</v>
       </c>
       <c r="H2" t="n">
-        <v>3.8939</v>
+        <v>3.8941</v>
       </c>
       <c r="I2" t="n">
-        <v>1.0648</v>
+        <v>1.0749</v>
       </c>
       <c r="J2" t="n">
-        <v>6.0466</v>
+        <v>6.231</v>
       </c>
       <c r="K2" t="n">
-        <v>5.9304</v>
+        <v>6.0431</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1161000000000003</v>
+        <v>0.1880000000000002</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.0878</v>
+        <v>-1.262</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.0365</v>
+        <v>-2.1489</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9487</v>
+        <v>0.8868</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.8194000000000001</v>
+        <v>-0.8097999999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>-4.097</v>
+        <v>-4.049</v>
       </c>
       <c r="R2" t="n">
-        <v>3.2776</v>
+        <v>3.2392</v>
       </c>
       <c r="S2" t="n">
-        <v>-4.452</v>
+        <v>-4.4136</v>
       </c>
       <c r="T2" t="n">
-        <v>-2.8165</v>
+        <v>-2.7534</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.6356</v>
+        <v>-1.6602</v>
       </c>
       <c r="V2" t="n">
-        <v>3.6658</v>
+        <v>3.7025</v>
       </c>
       <c r="W2" t="n">
-        <v>5.2065</v>
+        <v>5.2627</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.5407</v>
+        <v>-1.5602</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0737</v>
+        <v>2.1105</v>
       </c>
       <c r="E3" t="n">
-        <v>6.3238</v>
+        <v>6.5481</v>
       </c>
       <c r="F3" t="n">
-        <v>-4.25</v>
+        <v>-4.4376</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.2444</v>
+        <v>-0.2573</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.07189999999999999</v>
+        <v>-0.04120000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1724</v>
+        <v>-0.2161</v>
       </c>
       <c r="J3" t="n">
-        <v>4.3975</v>
+        <v>4.5318</v>
       </c>
       <c r="K3" t="n">
-        <v>3.0791</v>
+        <v>3.1963</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3185</v>
+        <v>1.3354</v>
       </c>
       <c r="M3" t="n">
-        <v>-4.6419</v>
+        <v>-4.7889</v>
       </c>
       <c r="N3" t="n">
-        <v>-3.151</v>
+        <v>-3.2374</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.4909</v>
+        <v>-1.5515</v>
       </c>
       <c r="P3" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0484</v>
+        <v>2.0246</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.2479</v>
+        <v>-2.2151</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8334</v>
+        <v>-0.7928999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.4145</v>
+        <v>-1.4222</v>
       </c>
       <c r="V3" t="n">
-        <v>3.5418</v>
+        <v>3.5706</v>
       </c>
       <c r="W3" t="n">
-        <v>3.7839</v>
+        <v>3.8215</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="4">
@@ -721,31 +721,31 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4709</v>
+        <v>1.4853</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4709</v>
+        <v>1.4853</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>1.4709</v>
+        <v>1.4853</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8782000000000001</v>
+        <v>0.8889</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5927</v>
+        <v>0.5963000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>1.4709</v>
+        <v>1.4853</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8782000000000001</v>
+        <v>0.8889</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5927</v>
+        <v>0.5963000000000001</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -799,67 +799,67 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.321</v>
+        <v>-0.3673000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1667</v>
+        <v>1.2992</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.4878</v>
+        <v>-1.6665</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5667</v>
+        <v>1.5097</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8302999999999999</v>
+        <v>0.8114000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7365</v>
+        <v>0.6982</v>
       </c>
       <c r="J5" t="n">
-        <v>2.844</v>
+        <v>2.9103</v>
       </c>
       <c r="K5" t="n">
-        <v>2.1973</v>
+        <v>2.2508</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6466999999999999</v>
+        <v>0.6596</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.2773</v>
+        <v>-1.4007</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.3669</v>
+        <v>-1.4393</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0897</v>
+        <v>0.0386</v>
       </c>
       <c r="P5" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0485</v>
+        <v>2.0245</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.4457</v>
+        <v>-2.426</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.1372</v>
+        <v>-1.1008</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.3086</v>
+        <v>-1.3252</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.4663</v>
+        <v>-0.4631999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>0.4842</v>
+        <v>0.5018</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.9505</v>
+        <v>-0.965</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.4489</v>
+        <v>-1.3873</v>
       </c>
       <c r="E6" t="n">
-        <v>2.8518</v>
+        <v>3.092</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.3007</v>
+        <v>-4.479200000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3745</v>
+        <v>1.3809</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2517</v>
+        <v>1.2644</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1227</v>
+        <v>0.1163000000000003</v>
       </c>
       <c r="J6" t="n">
-        <v>3.6501</v>
+        <v>3.7681</v>
       </c>
       <c r="K6" t="n">
-        <v>3.3154</v>
+        <v>3.3958</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3347</v>
+        <v>0.3722999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.2756</v>
+        <v>-2.3874</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.0637</v>
+        <v>-2.1314</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2119</v>
+        <v>-0.256</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.6388</v>
+        <v>-1.6196</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.0969</v>
+        <v>-4.0491</v>
       </c>
       <c r="R6" t="n">
-        <v>2.4581</v>
+        <v>2.4295</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.8196</v>
+        <v>-2.7761</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8334999999999999</v>
+        <v>-0.7928999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.9861</v>
+        <v>-1.9833</v>
       </c>
       <c r="V6" t="n">
-        <v>1.635</v>
+        <v>1.6276</v>
       </c>
       <c r="W6" t="n">
-        <v>4.132099999999999</v>
+        <v>4.165699999999999</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.4971</v>
+        <v>-2.5381</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.3591</v>
+        <v>-2.3463</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.6112</v>
+        <v>-1.4896</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7478</v>
+        <v>-0.8567</v>
       </c>
       <c r="G7" t="n">
-        <v>2.3503</v>
+        <v>2.3201</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1705000000000001</v>
+        <v>-0.1964000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>2.5208</v>
+        <v>2.5165</v>
       </c>
       <c r="J7" t="n">
-        <v>2.5663</v>
+        <v>2.6216</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6945999999999999</v>
+        <v>0.7296</v>
       </c>
       <c r="L7" t="n">
-        <v>1.8718</v>
+        <v>1.892</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.216</v>
+        <v>-0.3015</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.865</v>
+        <v>-0.926</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6489999999999999</v>
+        <v>0.6244999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.2533</v>
+        <v>-2.227</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.0727</v>
+        <v>-3.0368</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8193</v>
+        <v>0.8099000000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.3994</v>
+        <v>-1.3812</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4084</v>
+        <v>-0.3861</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9911</v>
+        <v>-0.9951</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0566</v>
+        <v>-1.0583</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.6965</v>
+        <v>-0.6883</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3602</v>
+        <v>-0.3699</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.5413</v>
+        <v>-2.5709</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0602</v>
+        <v>-1.0094</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4811</v>
+        <v>-1.5615</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.5244</v>
+        <v>-2.5408</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3095</v>
+        <v>-0.3159000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.2149</v>
+        <v>-2.2248</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.6352</v>
+        <v>-1.6025</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2811</v>
+        <v>-0.2582</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.354</v>
+        <v>-1.3444</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8892</v>
+        <v>-0.9381999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.02829999999999999</v>
+        <v>-0.05779999999999996</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8609</v>
+        <v>-0.8804</v>
       </c>
       <c r="P8" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.246</v>
+        <v>-0.2448</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.01529999999999998</v>
+        <v>-0.001900000000000013</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2306</v>
+        <v>-0.2428999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5903</v>
+        <v>-0.5951</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5903</v>
+        <v>0.5951</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.689</v>
+        <v>-2.6502</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7097</v>
+        <v>-1.3649</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9792000000000001</v>
+        <v>-1.2853</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1839</v>
+        <v>0.1469</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9478000000000001</v>
+        <v>-0.9487</v>
       </c>
       <c r="I9" t="n">
-        <v>1.1316</v>
+        <v>1.0958</v>
       </c>
       <c r="J9" t="n">
-        <v>1.6062</v>
+        <v>1.745</v>
       </c>
       <c r="K9" t="n">
-        <v>1.5626</v>
+        <v>1.6746</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04350000000000009</v>
+        <v>0.07050000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4224</v>
+        <v>-1.598</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.5104</v>
+        <v>-2.6233</v>
       </c>
       <c r="O9" t="n">
-        <v>1.088</v>
+        <v>1.0253</v>
       </c>
       <c r="P9" t="n">
-        <v>-3.6873</v>
+        <v>-3.6441</v>
       </c>
       <c r="Q9" t="n">
-        <v>-6.1454</v>
+        <v>-6.0736</v>
       </c>
       <c r="R9" t="n">
-        <v>2.4581</v>
+        <v>2.4295</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1766</v>
+        <v>0.1486</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5296000000000001</v>
+        <v>-0.485</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7061999999999999</v>
+        <v>0.6337</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6377999999999999</v>
+        <v>0.6983000000000001</v>
       </c>
       <c r="W9" t="n">
-        <v>3.3591</v>
+        <v>3.4486</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.7213</v>
+        <v>-2.7504</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.1061</v>
+        <v>-4.1285</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8966</v>
+        <v>-1.8711</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.2095</v>
+        <v>-2.2574</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.6176</v>
+        <v>-2.6373</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3403</v>
+        <v>-0.3551</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.2774</v>
+        <v>-2.2823</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.3155</v>
+        <v>-1.3051</v>
       </c>
       <c r="K10" t="n">
-        <v>0.078</v>
+        <v>0.0791</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3935</v>
+        <v>-1.3842</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.3022</v>
+        <v>-1.3322</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4184</v>
+        <v>-0.434</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8838</v>
+        <v>-0.8981</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5125999999999999</v>
+        <v>-0.5034000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5810999999999999</v>
+        <v>-0.5660000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>0.06840000000000002</v>
+        <v>0.06260000000000002</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.4633</v>
+        <v>-6.500500000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.931</v>
+        <v>-3.7304</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.5323</v>
+        <v>-2.7701</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.2433</v>
+        <v>-1.2617</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.8031</v>
+        <v>-1.7802</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5596</v>
+        <v>0.5186000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>2.1013</v>
+        <v>2.1976</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6786999999999999</v>
+        <v>0.7664</v>
       </c>
       <c r="L11" t="n">
-        <v>1.4225</v>
+        <v>1.4312</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.3446</v>
+        <v>-3.4593</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.4817</v>
+        <v>-2.5467</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.8629</v>
+        <v>-0.9126</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.2776</v>
+        <v>-3.2392</v>
       </c>
       <c r="Q11" t="n">
-        <v>-5.1212</v>
+        <v>-5.0613</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8436</v>
+        <v>1.8221</v>
       </c>
       <c r="S11" t="n">
-        <v>1.9478</v>
+        <v>1.9151</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1337</v>
+        <v>0.1657</v>
       </c>
       <c r="U11" t="n">
-        <v>1.8141</v>
+        <v>1.7494</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.89</v>
+        <v>-3.9148</v>
       </c>
       <c r="W11" t="n">
-        <v>-1.0447</v>
+        <v>-1.0325</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.8453</v>
+        <v>-2.8823</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-13.133</v>
+        <v>-13.1565</v>
       </c>
       <c r="E12" t="n">
-        <v>-10.4415</v>
+        <v>-10.2437</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.6915</v>
+        <v>-2.9128</v>
       </c>
       <c r="G12" t="n">
-        <v>-8.8186</v>
+        <v>-8.854800000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.8837</v>
+        <v>-4.9014</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.9349</v>
+        <v>-3.9534</v>
       </c>
       <c r="J12" t="n">
-        <v>-7.396800000000001</v>
+        <v>-7.2944</v>
       </c>
       <c r="K12" t="n">
-        <v>-4.0461</v>
+        <v>-3.9768</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.3507</v>
+        <v>-3.3177</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.4217</v>
+        <v>-1.5604</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8375999999999999</v>
+        <v>-0.9246</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5841</v>
+        <v>-0.6358</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.6388</v>
+        <v>-1.6196</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.0969</v>
+        <v>-4.0491</v>
       </c>
       <c r="R12" t="n">
-        <v>2.4582</v>
+        <v>2.4294</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7866000000000001</v>
+        <v>-0.7778</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1283</v>
+        <v>-0.09050000000000002</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6583</v>
+        <v>-0.6873</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.889</v>
+        <v>-1.9043</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.0696</v>
+        <v>-3.0945</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>-26.164</v>
+        <v>-26.0636</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.497300000000004</v>
+        <v>-2.593100000000002</v>
       </c>
       <c r="F13" t="n">
-        <v>-21.6665</v>
+        <v>-23.4703</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.5433</v>
+        <v>-3.739999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.6727</v>
+        <v>-1.680099999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.8709</v>
+        <v>-2.06</v>
       </c>
       <c r="J13" t="n">
-        <v>14.3354</v>
+        <v>15.2887</v>
       </c>
       <c r="K13" t="n">
-        <v>14.0871</v>
+        <v>14.7896</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2483</v>
+        <v>0.4989999999999992</v>
       </c>
       <c r="M13" t="n">
-        <v>-17.8787</v>
+        <v>-19.0286</v>
       </c>
       <c r="N13" t="n">
-        <v>-15.7595</v>
+        <v>-16.4694</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.1191</v>
+        <v>-2.5592</v>
       </c>
       <c r="P13" t="n">
-        <v>-10.2426</v>
+        <v>-10.1224</v>
       </c>
       <c r="Q13" t="n">
-        <v>-28.6785</v>
+        <v>-28.3435</v>
       </c>
       <c r="R13" t="n">
-        <v>18.436</v>
+        <v>18.221</v>
       </c>
       <c r="S13" t="n">
-        <v>-12.7854</v>
+        <v>-12.6743</v>
       </c>
       <c r="T13" t="n">
-        <v>-7.1496</v>
+        <v>-6.803799999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-5.6361</v>
+        <v>-5.870500000000002</v>
       </c>
       <c r="V13" t="n">
-        <v>0.4075999999999986</v>
+        <v>0.4731000000000005</v>
       </c>
       <c r="W13" t="n">
-        <v>16.9955</v>
+        <v>17.2648</v>
       </c>
       <c r="X13" t="n">
-        <v>-16.588</v>
+        <v>-16.7917</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_LOBE HUESCA LA MAGIA.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_LOBE HUESCA LA MAGIA.xlsx
@@ -565,13 +565,13 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4481</v>
+        <v>5.2819</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6914</v>
+        <v>6.040900000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.2432</v>
+        <v>-0.7591000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>4.969</v>
@@ -610,13 +610,13 @@
         <v>3.2392</v>
       </c>
       <c r="S2" t="n">
-        <v>-4.4136</v>
+        <v>-2.5798</v>
       </c>
       <c r="T2" t="n">
-        <v>-2.7534</v>
+        <v>-1.4038</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.6602</v>
+        <v>-1.176</v>
       </c>
       <c r="V2" t="n">
         <v>3.7025</v>
@@ -643,13 +643,13 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1105</v>
+        <v>2.831</v>
       </c>
       <c r="E3" t="n">
-        <v>6.5481</v>
+        <v>6.4443</v>
       </c>
       <c r="F3" t="n">
-        <v>-4.4376</v>
+        <v>-3.6133</v>
       </c>
       <c r="G3" t="n">
         <v>-0.2573</v>
@@ -688,13 +688,13 @@
         <v>2.0246</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.2151</v>
+        <v>-1.4946</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7928999999999999</v>
+        <v>-0.8968</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.4222</v>
+        <v>-0.5978999999999999</v>
       </c>
       <c r="V3" t="n">
         <v>3.5706</v>
@@ -799,13 +799,13 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3673000000000001</v>
+        <v>-0.1538999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2992</v>
+        <v>1.4029</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.6665</v>
+        <v>-1.5568</v>
       </c>
       <c r="G5" t="n">
         <v>1.5097</v>
@@ -844,13 +844,13 @@
         <v>2.0245</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.426</v>
+        <v>-2.2125</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.1008</v>
+        <v>-0.9969</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.3252</v>
+        <v>-1.2156</v>
       </c>
       <c r="V5" t="n">
         <v>-0.4631999999999999</v>
@@ -877,13 +877,13 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.3873</v>
+        <v>-1.0359</v>
       </c>
       <c r="E6" t="n">
-        <v>3.092</v>
+        <v>2.6767</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.479200000000001</v>
+        <v>-3.7126</v>
       </c>
       <c r="G6" t="n">
         <v>1.3809</v>
@@ -922,13 +922,13 @@
         <v>2.4295</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.7761</v>
+        <v>-2.4247</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7928999999999999</v>
+        <v>-1.2082</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.9833</v>
+        <v>-1.2166</v>
       </c>
       <c r="V6" t="n">
         <v>1.6276</v>
@@ -955,13 +955,13 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.3463</v>
+        <v>-1.7238</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.4896</v>
+        <v>-1.3858</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8567</v>
+        <v>-0.3381</v>
       </c>
       <c r="G7" t="n">
         <v>2.3201</v>
@@ -1000,13 +1000,13 @@
         <v>0.8099000000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.3812</v>
+        <v>-0.7586999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3861</v>
+        <v>-0.2823</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9951</v>
+        <v>-0.4765</v>
       </c>
       <c r="V7" t="n">
         <v>-1.0583</v>
@@ -1033,13 +1033,13 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.5709</v>
+        <v>-2.4727</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0094</v>
+        <v>-0.9056</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.5615</v>
+        <v>-1.5672</v>
       </c>
       <c r="G8" t="n">
         <v>-2.5408</v>
@@ -1078,13 +1078,13 @@
         <v>0.8098</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2448</v>
+        <v>-0.1467</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.001900000000000013</v>
+        <v>0.1019</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2428999999999999</v>
+        <v>-0.2485</v>
       </c>
       <c r="V8" t="n">
         <v>-0.5951</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. FRITZ</t>
+          <t>P. SUAREZ CUSTODIO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6502</v>
+        <v>-3.892</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3649</v>
+        <v>-1.6635</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2853</v>
+        <v>-2.2286</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1469</v>
+        <v>-2.6373</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9487</v>
+        <v>-0.3551</v>
       </c>
       <c r="I9" t="n">
-        <v>1.0958</v>
+        <v>-2.2823</v>
       </c>
       <c r="J9" t="n">
-        <v>1.745</v>
+        <v>-1.3051</v>
       </c>
       <c r="K9" t="n">
-        <v>1.6746</v>
+        <v>0.0791</v>
       </c>
       <c r="L9" t="n">
-        <v>0.07050000000000001</v>
+        <v>-1.3842</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.598</v>
+        <v>-1.3322</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.6233</v>
+        <v>-0.434</v>
       </c>
       <c r="O9" t="n">
-        <v>1.0253</v>
+        <v>-0.8981</v>
       </c>
       <c r="P9" t="n">
-        <v>-3.6441</v>
+        <v>0.2025</v>
       </c>
       <c r="Q9" t="n">
-        <v>-6.0736</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.4295</v>
+        <v>0.2025</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1486</v>
+        <v>-0.267</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.485</v>
+        <v>-0.3583</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6337</v>
+        <v>0.09140000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6983000000000001</v>
+        <v>-1.1902</v>
       </c>
       <c r="W9" t="n">
-        <v>3.4486</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.7504</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. SUAREZ CUSTODIO</t>
+          <t>J. FRITZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.1285</v>
+        <v>-3.9817</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8711</v>
+        <v>-1.884</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.2574</v>
+        <v>-2.0978</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.6373</v>
+        <v>0.1469</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3551</v>
+        <v>-0.9487</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.2823</v>
+        <v>1.0958</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.3051</v>
+        <v>1.745</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0791</v>
+        <v>1.6746</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3842</v>
+        <v>0.07050000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.3322</v>
+        <v>-1.598</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.434</v>
+        <v>-2.6233</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8981</v>
+        <v>1.0253</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2025</v>
+        <v>-3.6441</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-6.0736</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2025</v>
+        <v>2.4295</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5034000000000001</v>
+        <v>-1.1829</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5660000000000001</v>
+        <v>-1.0041</v>
       </c>
       <c r="U10" t="n">
-        <v>0.06260000000000002</v>
+        <v>-0.1788000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.1902</v>
+        <v>0.6983000000000001</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>3.4486</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.1902</v>
+        <v>-2.7504</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.500500000000001</v>
+        <v>-7.832</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.7304</v>
+        <v>-4.2495</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.7701</v>
+        <v>-3.5825</v>
       </c>
       <c r="G11" t="n">
         <v>-1.2617</v>
@@ -1312,13 +1312,13 @@
         <v>1.8221</v>
       </c>
       <c r="S11" t="n">
-        <v>1.9151</v>
+        <v>0.5834999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1657</v>
+        <v>-0.3534</v>
       </c>
       <c r="U11" t="n">
-        <v>1.7494</v>
+        <v>0.9369999999999999</v>
       </c>
       <c r="V11" t="n">
         <v>-3.9148</v>
@@ -1345,13 +1345,13 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-13.1565</v>
+        <v>-13.1855</v>
       </c>
       <c r="E12" t="n">
-        <v>-10.2437</v>
+        <v>-10.5552</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.9128</v>
+        <v>-2.6303</v>
       </c>
       <c r="G12" t="n">
         <v>-8.854800000000001</v>
@@ -1390,13 +1390,13 @@
         <v>2.4294</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7778</v>
+        <v>-0.8067</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.09050000000000002</v>
+        <v>-0.4019</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6873</v>
+        <v>-0.4048</v>
       </c>
       <c r="V12" t="n">
         <v>-1.9043</v>
@@ -1423,16 +1423,16 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>-26.0636</v>
+        <v>-24.6793</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.593100000000002</v>
+        <v>-2.593499999999998</v>
       </c>
       <c r="F13" t="n">
-        <v>-23.4703</v>
+        <v>-22.0863</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.739999999999999</v>
+        <v>-3.740000000000001</v>
       </c>
       <c r="H13" t="n">
         <v>-1.680099999999999</v>
@@ -1456,7 +1456,7 @@
         <v>-16.4694</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.5592</v>
+        <v>-2.559200000000001</v>
       </c>
       <c r="P13" t="n">
         <v>-10.1224</v>
@@ -1468,16 +1468,16 @@
         <v>18.221</v>
       </c>
       <c r="S13" t="n">
-        <v>-12.6743</v>
+        <v>-11.2901</v>
       </c>
       <c r="T13" t="n">
-        <v>-6.803799999999999</v>
+        <v>-6.803800000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-5.870500000000002</v>
+        <v>-4.4863</v>
       </c>
       <c r="V13" t="n">
-        <v>0.4731000000000005</v>
+        <v>0.4730999999999996</v>
       </c>
       <c r="W13" t="n">
         <v>17.2648</v>
